--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -740,9 +740,23 @@
         <v>2026-08-10</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">la planet electrique </v>
+      </c>
+      <c r="B3" t="str">
+        <v>chemin du câble</v>
+      </c>
+      <c r="C3">
+        <v>582</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-09-18</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -759,10 +773,53 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:D3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>type</v>
+      </c>
+      <c r="B1" t="str">
+        <v>date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>montant</v>
+      </c>
+      <c r="D1" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v xml:space="preserve">logement </v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C2">
+        <v>1800</v>
+      </c>
+      <c r="D2" t="str">
+        <v xml:space="preserve">logement appartement </v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">déplacement jerba  </v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve">frais du déplacement rafik </v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -793,13 +850,13 @@
         <v>rafik</v>
       </c>
       <c r="B2" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1010</v>
+        <v>1111</v>
       </c>
       <c r="E2" t="str">
         <v>dev</v>
@@ -1352,7 +1409,7 @@
         <v xml:space="preserve">câblage hors armoire sur site </v>
       </c>
       <c r="D3">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -701,16 +701,84 @@
         <v>8466.255</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B13" t="str">
+        <v>matériel installation+ chemin du câble</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2602136</v>
+      </c>
+      <c r="D13" t="str">
+        <v>-</v>
+      </c>
+      <c r="E13">
+        <v>3368.676</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B14" t="str">
+        <v>chemin de cable</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2602106</v>
+      </c>
+      <c r="D14" t="str">
+        <v>-</v>
+      </c>
+      <c r="E14">
+        <v>357.661</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Aouin et fils</v>
+      </c>
+      <c r="B15" t="str">
+        <v xml:space="preserve">câble signale </v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>37</v>
+      </c>
+      <c r="E15">
+        <v>21811</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Automation Technics</v>
+      </c>
+      <c r="B16" t="str">
+        <v xml:space="preserve">câble partibus 100 m </v>
+      </c>
+      <c r="C16" t="str">
+        <v>At2610-0302</v>
+      </c>
+      <c r="D16" t="str">
+        <v>38</v>
+      </c>
+      <c r="E16">
+        <v>1178.981</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -754,26 +822,183 @@
         <v>2026-09-18</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>boussaid</v>
+      </c>
+      <c r="B4" t="str">
+        <v>coude et fil</v>
+      </c>
+      <c r="C4">
+        <v>45.7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-10-29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>quincaillerie ajaj</v>
+      </c>
+      <c r="B5" t="str">
+        <v>boulant +tube +..</v>
+      </c>
+      <c r="C5">
+        <v>31.9</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-09-22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>quincaillerie ajaj</v>
+      </c>
+      <c r="B6" t="str">
+        <v>rondel + boulant ....</v>
+      </c>
+      <c r="C6">
+        <v>89</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-09-22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>quincaillerie ajaj</v>
+      </c>
+      <c r="B7" t="str">
+        <v>disque +rondel + ...</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-09-23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SRiDi</v>
+      </c>
+      <c r="B8" t="str">
+        <v>coude +crepe</v>
+      </c>
+      <c r="C8">
+        <v>17.1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-09-21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>quincaillerie ajaj</v>
+      </c>
+      <c r="B9" t="str">
+        <v>corge 25 +corge 32 +vis</v>
+      </c>
+      <c r="C9">
+        <v>14.25</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-10-30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="B10" t="str">
+        <v xml:space="preserve">électricité + charge </v>
+      </c>
+      <c r="C10">
+        <v>4000</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-10-01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="B11" t="str">
+        <v xml:space="preserve">câble Profibus 100 m </v>
+      </c>
+      <c r="C11">
+        <v>1178.981</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-09-30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>montant</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B2">
+        <v>720</v>
+      </c>
+      <c r="C2" t="str">
+        <v>rafik et houcem</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>rochdi</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4" t="str">
+        <v xml:space="preserve">rafik et houcem </v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -805,28 +1030,70 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">déplacement jerba  </v>
+        <v>logement</v>
       </c>
       <c r="B3" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C3">
+        <v>1800</v>
+      </c>
+      <c r="D3" t="str">
+        <v>logement a jerba 12 jours plus</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="C4">
+        <v>250</v>
+      </c>
+      <c r="D4" t="str">
+        <v>déplacement vers jerba livraison câbles  selon prix jerba transport  - 237</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Gazoil carte</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="C5">
+        <v>610</v>
+      </c>
+      <c r="D5" t="str">
+        <v>gazoil du carte + 100 dt   (cout interne )</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">location </v>
+      </c>
+      <c r="B6" t="str">
         <v>2026-09-21</v>
       </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-      <c r="D3" t="str">
-        <v xml:space="preserve">frais du déplacement rafik </v>
+      <c r="C6">
+        <v>3000</v>
+      </c>
+      <c r="D6" t="str">
+        <v>camion 25 jours (cout interne ) - 204</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -850,16 +1117,16 @@
         <v>rafik</v>
       </c>
       <c r="B2" t="str">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1111</v>
+        <v>3636</v>
       </c>
       <c r="E2" t="str">
-        <v>dev</v>
+        <v>dev + 25 jours mise en service</v>
       </c>
     </row>
     <row r="3">
@@ -879,16 +1146,101 @@
         <v>dev</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B4" t="str">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4">
+        <v>2000</v>
+      </c>
+      <c r="E4" t="str">
+        <v>pm</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>sondes</v>
+      </c>
+      <c r="B5" t="str">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>435</v>
+      </c>
+      <c r="E5" t="str">
+        <v>achat</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>faten</v>
+      </c>
+      <c r="B6" t="str">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>435</v>
+      </c>
+      <c r="E6" t="str">
+        <v>achat</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>manel</v>
+      </c>
+      <c r="B7" t="str">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>290</v>
+      </c>
+      <c r="E7" t="str">
+        <v>achat</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>houcem</v>
+      </c>
+      <c r="B8" t="str">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>500</v>
+      </c>
+      <c r="E8" t="str">
+        <v xml:space="preserve">technicien </v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1140,9 +1492,93 @@
         <v>25.4</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C15" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D15">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D16">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Aouin</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D17">
+        <v>6477.983</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Aouin</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="C18" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D18">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Aouin</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="C19" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D19">
+        <v>7615</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AVEVA</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="C20" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D20">
+        <v>95942</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1315,13 +1751,13 @@
         <v>2026-09-21</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-09-24</v>
+        <v>2026-10-15</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1330,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="str">
-        <v>A_VENIR</v>
+        <v>EN_COURS</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H8" t="str">
         <v>A_VENIR</v>
@@ -1406,10 +1842,10 @@
         <v>mansour 53.185.773</v>
       </c>
       <c r="C3" t="str">
-        <v xml:space="preserve">câblage hors armoire sur site </v>
+        <v>câblage hors armoire sur site (rawed équipe)</v>
       </c>
       <c r="D3">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -452,28 +452,28 @@
         <v xml:space="preserve">redondance </v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>2026-02-05</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>2026-04-30</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2026-10-31</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="str">
-        <v>A_VENIR</v>
+        <v>EN_COURS</v>
       </c>
     </row>
   </sheetData>
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -740,7 +740,7 @@
         <v>Aouin et fils</v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve">câble signale </v>
+        <v>câble signale 3900 m</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -769,9 +769,60 @@
         <v>1178.981</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Aouin et fils</v>
+      </c>
+      <c r="B17" t="str">
+        <v>cuivre - enbout - vis</v>
+      </c>
+      <c r="C17" t="str">
+        <v>202602443</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>automation technics</v>
+      </c>
+      <c r="B18" t="str">
+        <v>câble Profibus 100 m</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>1178.98</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Hammami transport</v>
+      </c>
+      <c r="B19" t="str">
+        <v xml:space="preserve">transport </v>
+      </c>
+      <c r="C19" t="str">
+        <v>05411</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1417,7 +1468,7 @@
         <v>2026-10-01</v>
       </c>
       <c r="C11" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="D11">
         <v>7141</v>

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -464,10 +464,10 @@
         <v/>
       </c>
       <c r="G2">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -820,9 +820,77 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Aouin et fils</v>
+      </c>
+      <c r="B20" t="str">
+        <v>câble signale 1200</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>39</v>
+      </c>
+      <c r="E20">
+        <v>6644.777</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LA PLANET ELECTRIQUE</v>
+      </c>
+      <c r="B21" t="str">
+        <v xml:space="preserve">460 câble signale </v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>40</v>
+      </c>
+      <c r="E21">
+        <v>2586.082</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B22" t="str">
+        <v>élément électriques 7/10/2026</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2602301</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>157.58</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B23" t="str">
+        <v>en cours devis</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>3002</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1015,7 +1083,7 @@
         <v>720</v>
       </c>
       <c r="C2" t="str">
-        <v>rafik et houcem</v>
+        <v>rafik et houcem alimentation caisse</v>
       </c>
     </row>
     <row r="3">
@@ -1034,10 +1102,10 @@
         <v>2026-09-30</v>
       </c>
       <c r="B4">
-        <v>500</v>
+        <v>880</v>
       </c>
       <c r="C4" t="str">
-        <v xml:space="preserve">rafik et houcem </v>
+        <v>rafik et houcem alimentation caisse</v>
       </c>
     </row>
   </sheetData>
@@ -1081,58 +1149,58 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>logement</v>
+        <v xml:space="preserve">déplacement </v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-30</v>
       </c>
       <c r="C3">
-        <v>1800</v>
+        <v>250</v>
       </c>
       <c r="D3" t="str">
-        <v>logement a jerba 12 jours plus</v>
+        <v>déplacement vers jerba livraison câbles  selon prix jerba transport  - 237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">déplacement </v>
+        <v>Gazoil carte</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-22</v>
       </c>
       <c r="C4">
-        <v>250</v>
+        <v>610</v>
       </c>
       <c r="D4" t="str">
-        <v>déplacement vers jerba livraison câbles  selon prix jerba transport  - 237</v>
+        <v>gazoil du carte + 100 dt   (cout interne )</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Gazoil carte</v>
+        <v xml:space="preserve">location </v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C5">
-        <v>610</v>
+        <v>3000</v>
       </c>
       <c r="D5" t="str">
-        <v>gazoil du carte + 100 dt   (cout interne )</v>
+        <v>camion 25 jours (cout interne ) - 204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">location </v>
+        <v>logement</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-21</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C6">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="D6" t="str">
-        <v>camion 25 jours (cout interne ) - 204</v>
+        <v>logement 1 mois</v>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +1519,7 @@
         <v>AVEVA</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-30</v>
       </c>
       <c r="C10" t="str">
         <v>NON_PAYE</v>
@@ -1482,7 +1550,7 @@
         <v>2026-09-13</v>
       </c>
       <c r="C12" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="D12">
         <v>3352.64</v>
@@ -1896,7 +1964,7 @@
         <v>câblage hors armoire sur site (rawed équipe)</v>
       </c>
       <c r="D3">
-        <v>6000</v>
+        <v>7438.5</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -41,12 +41,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -464,10 +460,10 @@
         <v/>
       </c>
       <c r="G2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -495,7 +491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -706,7 +702,7 @@
         <v>cogen</v>
       </c>
       <c r="B13" t="str">
-        <v>matériel installation+ chemin du câble</v>
+        <v>matériel installation+ chemin du câble  26/09/2026</v>
       </c>
       <c r="C13" t="str">
         <v>2602136</v>
@@ -723,7 +719,7 @@
         <v>cogen</v>
       </c>
       <c r="B14" t="str">
-        <v>chemin de cable</v>
+        <v>chemin de cable 21/09/2026</v>
       </c>
       <c r="C14" t="str">
         <v>2602106</v>
@@ -876,28 +872,45 @@
         <v>cogen</v>
       </c>
       <c r="B23" t="str">
-        <v>en cours devis</v>
+        <v>élément électrique 16/10/2026</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>2602364</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>3002</v>
+        <v>3206.565</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>cogen</v>
+      </c>
+      <c r="B24" t="str">
+        <v>element 17/10/2026</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2602376</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>318.98</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1053,16 +1066,30 @@
         <v>2026-09-30</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">la planet électrique </v>
+      </c>
+      <c r="B12" t="str">
+        <v>câble 460 m</v>
+      </c>
+      <c r="C12">
+        <v>2585</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1108,16 +1135,27 @@
         <v>rafik et houcem alimentation caisse</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="B5">
+        <v>500</v>
+      </c>
+      <c r="C5" t="str">
+        <v>rafik et houcem caisse alimentation caisse</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1203,9 +1241,51 @@
         <v>logement 1 mois</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>lacation</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="C7">
+        <v>1500</v>
+      </c>
+      <c r="D7" t="str">
+        <v>location express 237</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">carte gazoil </v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+      <c r="D8" t="str">
+        <v>500 dt</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">carte gazoil </v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9" t="str">
+        <v xml:space="preserve">200 dt </v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1270,13 +1350,13 @@
         <v>rochdi</v>
       </c>
       <c r="B4" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="E4" t="str">
         <v>pm</v>
@@ -1359,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1516,30 +1596,39 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AVEVA</v>
+        <v>SAIDANA</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="C10" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="D10">
-        <v>95942</v>
+        <v>7141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SAIDANA</v>
+        <v>LA PLANET ELECTRIQUE</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-13</v>
       </c>
       <c r="C11" t="str">
         <v>PAYE</v>
       </c>
       <c r="D11">
-        <v>7141</v>
+        <v>3352.64</v>
+      </c>
+      <c r="E11" t="str">
+        <v>PAY-1789134017086-1</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>33.87</v>
       </c>
     </row>
     <row r="12">
@@ -1547,22 +1636,22 @@
         <v>LA PLANET ELECTRIQUE</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-13</v>
+        <v>2026-10-13</v>
       </c>
       <c r="C12" t="str">
         <v>PAYE</v>
       </c>
       <c r="D12">
-        <v>3352.64</v>
+        <v>2514.48</v>
       </c>
       <c r="E12" t="str">
-        <v>PAY-1789134017086-1</v>
+        <v>PAY-1789134017086-2</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12">
-        <v>33.87</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="13">
@@ -1570,7 +1659,7 @@
         <v>LA PLANET ELECTRIQUE</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-10-13</v>
+        <v>2026-11-12</v>
       </c>
       <c r="C13" t="str">
         <v>NON_PAYE</v>
@@ -1579,7 +1668,7 @@
         <v>2514.48</v>
       </c>
       <c r="E13" t="str">
-        <v>PAY-1789134017086-2</v>
+        <v>PAY-1789134017086-3</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1590,25 +1679,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LA PLANET ELECTRIQUE</v>
+        <v>cogen</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-11-12</v>
+        <v>2026-09-28</v>
       </c>
       <c r="C14" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="D14">
-        <v>2514.48</v>
-      </c>
-      <c r="E14" t="str">
-        <v>PAY-1789134017086-3</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14">
-        <v>25.4</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="15">
@@ -1616,27 +1696,27 @@
         <v>cogen</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C15" t="str">
         <v>PAYE</v>
       </c>
       <c r="D15">
-        <v>3350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>cogen</v>
+        <v>Aouin</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="C16" t="str">
         <v>PAYE</v>
       </c>
       <c r="D16">
-        <v>357</v>
+        <v>6477.983</v>
       </c>
     </row>
     <row r="17">
@@ -1644,13 +1724,13 @@
         <v>Aouin</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-30</v>
       </c>
       <c r="C17" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="D17">
-        <v>6477.983</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="18">
@@ -1658,46 +1738,60 @@
         <v>Aouin</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-30</v>
       </c>
       <c r="C18" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="D18">
-        <v>7500</v>
+        <v>7615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Aouin</v>
+        <v>AVEVA</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-11-30</v>
+        <v>2026-10-30</v>
       </c>
       <c r="C19" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="D19">
-        <v>7615</v>
+        <v>95942</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>AVEVA</v>
+        <v>cogen</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-19</v>
       </c>
       <c r="C20" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D20">
+        <v>3646.27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Aouin</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2027-01-13</v>
+      </c>
+      <c r="C21" t="str">
         <v>NON_PAYE</v>
       </c>
-      <c r="D20">
-        <v>95942</v>
+      <c r="D21">
+        <v>6644.777</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1873,19 +1967,19 @@
         <v>2026-10-15</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>2026-11-19</v>
       </c>
       <c r="E7">
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="H7" t="str">
-        <v>EN_COURS</v>
+        <v>EN_RETARD</v>
       </c>
     </row>
     <row r="8">

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -460,16 +460,16 @@
         <v/>
       </c>
       <c r="G2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="str">
-        <v>EN_COURS</v>
+        <v>A_SURVEILLER</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -460,10 +460,10 @@
         <v/>
       </c>
       <c r="G2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -491,7 +491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -901,9 +901,26 @@
         <v>318.98</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Automation Technics</v>
+      </c>
+      <c r="B25" t="str">
+        <v xml:space="preserve">câble Profibus </v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>1167.201</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1439,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1789,9 +1806,23 @@
         <v>6644.777</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Automation Technics</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2027-01-20</v>
+      </c>
+      <c r="C22" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D22">
+        <v>1167.201</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G22"/>
   </ignoredErrors>
 </worksheet>
 </file>
